--- a/Src/Data/Tables/TeleporterDefine.xlsx
+++ b/Src/Data/Tables/TeleporterDefine.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>传送目标</t>
   </si>
@@ -102,7 +102,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -292,11 +292,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -309,20 +304,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -348,7 +329,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -538,24 +519,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -816,35 +779,35 @@
     <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -860,18 +823,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1018,8 +969,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A3:F13" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:F13" etc:filterBottomFollowUsedRange="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A3:F15" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:F15" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Key" dataDxfId="0"/>
     <tableColumn id="3" name="ID" dataDxfId="1"/>
@@ -1319,7 +1270,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultColWidth="16.2857142857143" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="11" style="2" customWidth="1"/>
@@ -1498,7 +1449,7 @@
         <v>4</v>
       </c>
       <c r="E10" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="4"/>
@@ -1515,41 +1466,75 @@
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="8">
+      <c r="A12" s="1">
         <v>9</v>
       </c>
       <c r="B12" s="2">
         <v>9</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="8">
+      <c r="D12" s="6"/>
+      <c r="E12" s="1">
         <v>5</v>
       </c>
-      <c r="F12" s="9"/>
+      <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="8">
+      <c r="A13" s="1">
         <v>10</v>
       </c>
       <c r="B13" s="2">
         <v>10</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="10">
+      <c r="D13" s="6"/>
+      <c r="E13" s="2">
         <v>5</v>
       </c>
-      <c r="F13" s="11"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="1">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2">
+        <v>11</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="6">
+        <v>4</v>
+      </c>
+      <c r="E14" s="1">
+        <v>4</v>
+      </c>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="1">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2">
+        <v>12</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="2">
+        <v>4</v>
+      </c>
+      <c r="F15" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
